--- a/precios_mayoristas_PRO_x12.xlsx
+++ b/precios_mayoristas_PRO_x12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A A CATÁLOGOS\1A CATÁLOGO MAYORISTA FINAL 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F484E4-24A2-49F1-BB64-1279C58C0981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86AA161-1098-4D3B-87D0-A93AA1A05524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="500">
   <si>
     <t>Nombre del producto</t>
   </si>
@@ -2860,6 +2860,18 @@
   </si>
   <si>
     <t>Color</t>
+  </si>
+  <si>
+    <t>DISFRACES PARA NENES</t>
+  </si>
+  <si>
+    <t>DISFRACES DE ANIMALITOS</t>
+  </si>
+  <si>
+    <t>TÍTERES DE MANO</t>
+  </si>
+  <si>
+    <t>TEATROS CON TÍTERES</t>
   </si>
 </sst>
 </file>
@@ -4406,6 +4418,9 @@
       <c r="A49" t="s">
         <v>60</v>
       </c>
+      <c r="B49" t="s">
+        <v>458</v>
+      </c>
       <c r="C49">
         <v>22</v>
       </c>
@@ -4426,6 +4441,9 @@
       <c r="A50" t="s">
         <v>61</v>
       </c>
+      <c r="B50" t="s">
+        <v>458</v>
+      </c>
       <c r="C50">
         <v>2</v>
       </c>
@@ -4446,6 +4464,9 @@
       <c r="A51" t="s">
         <v>62</v>
       </c>
+      <c r="B51" t="s">
+        <v>458</v>
+      </c>
       <c r="C51">
         <v>3</v>
       </c>
@@ -4466,6 +4487,9 @@
       <c r="A52" t="s">
         <v>63</v>
       </c>
+      <c r="B52" t="s">
+        <v>458</v>
+      </c>
       <c r="C52">
         <v>1</v>
       </c>
@@ -4486,6 +4510,9 @@
       <c r="A53" t="s">
         <v>64</v>
       </c>
+      <c r="B53" t="s">
+        <v>458</v>
+      </c>
       <c r="C53">
         <v>20</v>
       </c>
@@ -4506,6 +4533,9 @@
       <c r="A54" t="s">
         <v>65</v>
       </c>
+      <c r="B54" t="s">
+        <v>458</v>
+      </c>
       <c r="C54">
         <v>19</v>
       </c>
@@ -4526,6 +4556,9 @@
       <c r="A55" t="s">
         <v>491</v>
       </c>
+      <c r="B55" t="s">
+        <v>458</v>
+      </c>
       <c r="C55">
         <v>21</v>
       </c>
@@ -4546,6 +4579,9 @@
       <c r="A56" t="s">
         <v>66</v>
       </c>
+      <c r="B56" t="s">
+        <v>458</v>
+      </c>
       <c r="C56">
         <v>4</v>
       </c>
@@ -4566,6 +4602,9 @@
       <c r="A57" t="s">
         <v>67</v>
       </c>
+      <c r="B57" t="s">
+        <v>458</v>
+      </c>
       <c r="C57">
         <v>6</v>
       </c>
@@ -4586,6 +4625,9 @@
       <c r="A58" t="s">
         <v>68</v>
       </c>
+      <c r="B58" t="s">
+        <v>458</v>
+      </c>
       <c r="C58">
         <v>5</v>
       </c>
@@ -4606,6 +4648,9 @@
       <c r="A59" t="s">
         <v>69</v>
       </c>
+      <c r="B59" t="s">
+        <v>458</v>
+      </c>
       <c r="C59">
         <v>7</v>
       </c>
@@ -4626,6 +4671,9 @@
       <c r="A60" t="s">
         <v>70</v>
       </c>
+      <c r="B60" t="s">
+        <v>458</v>
+      </c>
       <c r="C60">
         <v>8</v>
       </c>
@@ -4646,6 +4694,9 @@
       <c r="A61" t="s">
         <v>71</v>
       </c>
+      <c r="B61" t="s">
+        <v>458</v>
+      </c>
       <c r="C61">
         <v>9</v>
       </c>
@@ -4666,6 +4717,9 @@
       <c r="A62" t="s">
         <v>72</v>
       </c>
+      <c r="B62" t="s">
+        <v>458</v>
+      </c>
       <c r="C62">
         <v>15</v>
       </c>
@@ -4686,6 +4740,9 @@
       <c r="A63" t="s">
         <v>73</v>
       </c>
+      <c r="B63" t="s">
+        <v>458</v>
+      </c>
       <c r="C63">
         <v>16</v>
       </c>
@@ -4706,6 +4763,9 @@
       <c r="A64" t="s">
         <v>74</v>
       </c>
+      <c r="B64" t="s">
+        <v>458</v>
+      </c>
       <c r="C64">
         <v>17</v>
       </c>
@@ -4726,6 +4786,9 @@
       <c r="A65" t="s">
         <v>75</v>
       </c>
+      <c r="B65" t="s">
+        <v>458</v>
+      </c>
       <c r="C65">
         <v>18</v>
       </c>
@@ -4746,6 +4809,9 @@
       <c r="A66" t="s">
         <v>76</v>
       </c>
+      <c r="B66" t="s">
+        <v>458</v>
+      </c>
       <c r="C66">
         <v>23</v>
       </c>
@@ -5306,6 +5372,9 @@
       <c r="A88" t="s">
         <v>79</v>
       </c>
+      <c r="B88" t="s">
+        <v>437</v>
+      </c>
       <c r="C88">
         <v>18</v>
       </c>
@@ -5329,6 +5398,9 @@
       <c r="A89" t="s">
         <v>80</v>
       </c>
+      <c r="B89" t="s">
+        <v>437</v>
+      </c>
       <c r="C89">
         <v>16</v>
       </c>
@@ -5352,6 +5424,9 @@
       <c r="A90" t="s">
         <v>81</v>
       </c>
+      <c r="B90" t="s">
+        <v>437</v>
+      </c>
       <c r="C90">
         <v>15</v>
       </c>
@@ -5375,6 +5450,9 @@
       <c r="A91" t="s">
         <v>82</v>
       </c>
+      <c r="B91" t="s">
+        <v>437</v>
+      </c>
       <c r="C91">
         <v>13</v>
       </c>
@@ -5398,6 +5476,9 @@
       <c r="A92" t="s">
         <v>83</v>
       </c>
+      <c r="B92" t="s">
+        <v>437</v>
+      </c>
       <c r="C92">
         <v>8</v>
       </c>
@@ -5421,6 +5502,9 @@
       <c r="A93" t="s">
         <v>84</v>
       </c>
+      <c r="B93" t="s">
+        <v>437</v>
+      </c>
       <c r="C93">
         <v>12</v>
       </c>
@@ -5444,6 +5528,9 @@
       <c r="A94" t="s">
         <v>85</v>
       </c>
+      <c r="B94" t="s">
+        <v>437</v>
+      </c>
       <c r="C94">
         <v>9</v>
       </c>
@@ -5467,6 +5554,9 @@
       <c r="A95" t="s">
         <v>86</v>
       </c>
+      <c r="B95" t="s">
+        <v>437</v>
+      </c>
       <c r="C95">
         <v>11</v>
       </c>
@@ -5490,6 +5580,9 @@
       <c r="A96" t="s">
         <v>87</v>
       </c>
+      <c r="B96" t="s">
+        <v>437</v>
+      </c>
       <c r="C96">
         <v>7</v>
       </c>
@@ -5513,6 +5606,9 @@
       <c r="A97" t="s">
         <v>88</v>
       </c>
+      <c r="B97" t="s">
+        <v>437</v>
+      </c>
       <c r="C97">
         <v>6</v>
       </c>
@@ -5536,6 +5632,9 @@
       <c r="A98" t="s">
         <v>89</v>
       </c>
+      <c r="B98" t="s">
+        <v>437</v>
+      </c>
       <c r="C98">
         <v>10</v>
       </c>
@@ -5559,6 +5658,9 @@
       <c r="A99" t="s">
         <v>90</v>
       </c>
+      <c r="B99" t="s">
+        <v>437</v>
+      </c>
       <c r="C99">
         <v>17</v>
       </c>
@@ -5582,6 +5684,9 @@
       <c r="A100" t="s">
         <v>91</v>
       </c>
+      <c r="B100" t="s">
+        <v>437</v>
+      </c>
       <c r="C100">
         <v>14</v>
       </c>
@@ -5605,6 +5710,9 @@
       <c r="A101" t="s">
         <v>92</v>
       </c>
+      <c r="B101" t="s">
+        <v>437</v>
+      </c>
       <c r="C101">
         <v>3</v>
       </c>
@@ -5628,6 +5736,9 @@
       <c r="A102" t="s">
         <v>93</v>
       </c>
+      <c r="B102" t="s">
+        <v>437</v>
+      </c>
       <c r="C102">
         <v>4</v>
       </c>
@@ -5680,6 +5791,9 @@
       <c r="A104" t="s">
         <v>94</v>
       </c>
+      <c r="B104" t="s">
+        <v>437</v>
+      </c>
       <c r="C104">
         <v>1</v>
       </c>
@@ -5703,6 +5817,9 @@
       <c r="A105" t="s">
         <v>95</v>
       </c>
+      <c r="B105" t="s">
+        <v>437</v>
+      </c>
       <c r="C105">
         <v>2</v>
       </c>
@@ -5983,6 +6100,9 @@
       <c r="A116" t="s">
         <v>98</v>
       </c>
+      <c r="B116" t="s">
+        <v>496</v>
+      </c>
       <c r="D116">
         <v>18000</v>
       </c>
@@ -6003,6 +6123,9 @@
       <c r="A117" t="s">
         <v>99</v>
       </c>
+      <c r="B117" t="s">
+        <v>496</v>
+      </c>
       <c r="D117">
         <v>18000</v>
       </c>
@@ -6023,6 +6146,9 @@
       <c r="A118" t="s">
         <v>100</v>
       </c>
+      <c r="B118" t="s">
+        <v>496</v>
+      </c>
       <c r="D118">
         <v>22000</v>
       </c>
@@ -6043,6 +6169,9 @@
       <c r="A119" t="s">
         <v>101</v>
       </c>
+      <c r="B119" t="s">
+        <v>496</v>
+      </c>
       <c r="D119">
         <v>23500</v>
       </c>
@@ -6063,6 +6192,9 @@
       <c r="A120" t="s">
         <v>102</v>
       </c>
+      <c r="B120" t="s">
+        <v>496</v>
+      </c>
       <c r="D120">
         <v>23500</v>
       </c>
@@ -6083,6 +6215,9 @@
       <c r="A121" t="s">
         <v>106</v>
       </c>
+      <c r="B121" t="s">
+        <v>497</v>
+      </c>
       <c r="D121">
         <v>25200</v>
       </c>
@@ -6103,6 +6238,9 @@
       <c r="A122" t="s">
         <v>107</v>
       </c>
+      <c r="B122" t="s">
+        <v>497</v>
+      </c>
       <c r="D122">
         <v>23500</v>
       </c>
@@ -6123,6 +6261,9 @@
       <c r="A123" t="s">
         <v>108</v>
       </c>
+      <c r="B123" t="s">
+        <v>497</v>
+      </c>
       <c r="D123">
         <v>23500</v>
       </c>
@@ -6143,6 +6284,9 @@
       <c r="A124" t="s">
         <v>109</v>
       </c>
+      <c r="B124" t="s">
+        <v>497</v>
+      </c>
       <c r="D124">
         <v>23500</v>
       </c>
@@ -6163,6 +6307,9 @@
       <c r="A125" t="s">
         <v>110</v>
       </c>
+      <c r="B125" t="s">
+        <v>496</v>
+      </c>
       <c r="D125">
         <v>15000</v>
       </c>
@@ -6180,6 +6327,9 @@
       <c r="A126" t="s">
         <v>111</v>
       </c>
+      <c r="B126" t="s">
+        <v>496</v>
+      </c>
       <c r="D126">
         <v>15000</v>
       </c>
@@ -6197,6 +6347,9 @@
       <c r="A127" t="s">
         <v>112</v>
       </c>
+      <c r="B127" t="s">
+        <v>498</v>
+      </c>
       <c r="C127">
         <v>1</v>
       </c>
@@ -6214,6 +6367,9 @@
       <c r="A128" t="s">
         <v>113</v>
       </c>
+      <c r="B128" t="s">
+        <v>498</v>
+      </c>
       <c r="C128">
         <v>2</v>
       </c>
@@ -6255,6 +6411,9 @@
       <c r="A129" t="s">
         <v>114</v>
       </c>
+      <c r="B129" t="s">
+        <v>498</v>
+      </c>
       <c r="C129">
         <v>10</v>
       </c>
@@ -6275,6 +6434,9 @@
       <c r="A130" t="s">
         <v>115</v>
       </c>
+      <c r="B130" t="s">
+        <v>498</v>
+      </c>
       <c r="C130">
         <v>5</v>
       </c>
@@ -6304,6 +6466,9 @@
       <c r="A131" t="s">
         <v>116</v>
       </c>
+      <c r="B131" t="s">
+        <v>498</v>
+      </c>
       <c r="C131">
         <v>8</v>
       </c>
@@ -6321,6 +6486,9 @@
       <c r="A132" t="s">
         <v>117</v>
       </c>
+      <c r="B132" t="s">
+        <v>498</v>
+      </c>
       <c r="C132">
         <v>9</v>
       </c>
@@ -6338,6 +6506,9 @@
       <c r="A133" t="s">
         <v>118</v>
       </c>
+      <c r="B133" t="s">
+        <v>498</v>
+      </c>
       <c r="C133">
         <v>3</v>
       </c>
@@ -6355,6 +6526,9 @@
       <c r="A134" t="s">
         <v>119</v>
       </c>
+      <c r="B134" t="s">
+        <v>498</v>
+      </c>
       <c r="C134">
         <v>6</v>
       </c>
@@ -6372,6 +6546,9 @@
       <c r="A135" t="s">
         <v>120</v>
       </c>
+      <c r="B135" t="s">
+        <v>498</v>
+      </c>
       <c r="C135">
         <v>7</v>
       </c>
@@ -6389,6 +6566,9 @@
       <c r="A136" t="s">
         <v>121</v>
       </c>
+      <c r="B136" t="s">
+        <v>498</v>
+      </c>
       <c r="C136">
         <v>11</v>
       </c>
@@ -6406,6 +6586,9 @@
       <c r="A137" t="s">
         <v>122</v>
       </c>
+      <c r="B137" t="s">
+        <v>498</v>
+      </c>
       <c r="C137">
         <v>12</v>
       </c>
@@ -6423,6 +6606,9 @@
       <c r="A138" t="s">
         <v>123</v>
       </c>
+      <c r="B138" t="s">
+        <v>498</v>
+      </c>
       <c r="C138">
         <v>4</v>
       </c>
@@ -6440,6 +6626,9 @@
       <c r="A139" t="s">
         <v>124</v>
       </c>
+      <c r="B139" t="s">
+        <v>498</v>
+      </c>
       <c r="C139">
         <v>13</v>
       </c>
@@ -6469,6 +6658,9 @@
       <c r="A140" t="s">
         <v>125</v>
       </c>
+      <c r="B140" t="s">
+        <v>498</v>
+      </c>
       <c r="C140">
         <v>16</v>
       </c>
@@ -6486,6 +6678,9 @@
       <c r="A141" t="s">
         <v>126</v>
       </c>
+      <c r="B141" t="s">
+        <v>498</v>
+      </c>
       <c r="C141">
         <v>14</v>
       </c>
@@ -6521,6 +6716,9 @@
       <c r="A142" t="s">
         <v>127</v>
       </c>
+      <c r="B142" t="s">
+        <v>498</v>
+      </c>
       <c r="C142">
         <v>15</v>
       </c>
@@ -6538,6 +6736,9 @@
       <c r="A143" t="s">
         <v>128</v>
       </c>
+      <c r="B143" t="s">
+        <v>498</v>
+      </c>
       <c r="C143">
         <v>17</v>
       </c>
@@ -6579,6 +6780,9 @@
       <c r="A144" t="s">
         <v>129</v>
       </c>
+      <c r="B144" t="s">
+        <v>498</v>
+      </c>
       <c r="C144">
         <v>18</v>
       </c>
@@ -6596,6 +6800,9 @@
       <c r="A145" t="s">
         <v>130</v>
       </c>
+      <c r="B145" t="s">
+        <v>498</v>
+      </c>
       <c r="C145">
         <v>19</v>
       </c>
@@ -6613,6 +6820,9 @@
       <c r="A146" t="s">
         <v>131</v>
       </c>
+      <c r="B146" t="s">
+        <v>498</v>
+      </c>
       <c r="C146">
         <v>20</v>
       </c>
@@ -6633,6 +6843,9 @@
       <c r="A147" t="s">
         <v>132</v>
       </c>
+      <c r="B147" t="s">
+        <v>498</v>
+      </c>
       <c r="C147">
         <v>21</v>
       </c>
@@ -6650,6 +6863,9 @@
       <c r="A148" t="s">
         <v>133</v>
       </c>
+      <c r="B148" t="s">
+        <v>498</v>
+      </c>
       <c r="C148">
         <v>22</v>
       </c>
@@ -6667,6 +6883,9 @@
       <c r="A149" t="s">
         <v>134</v>
       </c>
+      <c r="B149" t="s">
+        <v>499</v>
+      </c>
       <c r="J149">
         <v>29800</v>
       </c>
@@ -6705,6 +6924,9 @@
       <c r="A150" t="s">
         <v>135</v>
       </c>
+      <c r="B150" t="s">
+        <v>499</v>
+      </c>
       <c r="J150">
         <v>29800</v>
       </c>
@@ -6731,6 +6953,9 @@
       <c r="A151" t="s">
         <v>136</v>
       </c>
+      <c r="B151" t="s">
+        <v>499</v>
+      </c>
       <c r="D151">
         <v>32980</v>
       </c>
@@ -6745,6 +6970,9 @@
       <c r="A152" t="s">
         <v>137</v>
       </c>
+      <c r="B152" t="s">
+        <v>499</v>
+      </c>
       <c r="D152">
         <v>36200</v>
       </c>
@@ -6759,6 +6987,9 @@
       <c r="A153" t="s">
         <v>138</v>
       </c>
+      <c r="B153" t="s">
+        <v>499</v>
+      </c>
       <c r="D153">
         <v>36800</v>
       </c>
@@ -6773,6 +7004,9 @@
       <c r="A154" t="s">
         <v>139</v>
       </c>
+      <c r="B154" t="s">
+        <v>499</v>
+      </c>
       <c r="D154">
         <v>36800</v>
       </c>
@@ -6787,6 +7021,9 @@
       <c r="A155" t="s">
         <v>140</v>
       </c>
+      <c r="B155" t="s">
+        <v>499</v>
+      </c>
       <c r="D155">
         <v>38200</v>
       </c>
@@ -6801,6 +7038,9 @@
       <c r="A156" t="s">
         <v>141</v>
       </c>
+      <c r="B156" t="s">
+        <v>499</v>
+      </c>
       <c r="D156">
         <v>36800</v>
       </c>
@@ -6815,6 +7055,9 @@
       <c r="A157" t="s">
         <v>142</v>
       </c>
+      <c r="B157" t="s">
+        <v>499</v>
+      </c>
       <c r="D157">
         <v>29800</v>
       </c>
@@ -6829,6 +7072,9 @@
       <c r="A158" t="s">
         <v>143</v>
       </c>
+      <c r="B158" t="s">
+        <v>499</v>
+      </c>
       <c r="J158">
         <v>36800</v>
       </c>
@@ -6852,6 +7098,9 @@
       <c r="A159" t="s">
         <v>144</v>
       </c>
+      <c r="B159" t="s">
+        <v>499</v>
+      </c>
       <c r="J159">
         <v>29800</v>
       </c>
@@ -6890,6 +7139,9 @@
       <c r="A160" t="s">
         <v>145</v>
       </c>
+      <c r="B160" t="s">
+        <v>499</v>
+      </c>
       <c r="D160">
         <v>36800</v>
       </c>
@@ -6904,6 +7156,9 @@
       <c r="A161" t="s">
         <v>146</v>
       </c>
+      <c r="B161" t="s">
+        <v>499</v>
+      </c>
       <c r="J161">
         <v>36800</v>
       </c>
@@ -6927,6 +7182,9 @@
       <c r="A162" t="s">
         <v>147</v>
       </c>
+      <c r="B162" t="s">
+        <v>499</v>
+      </c>
       <c r="D162">
         <v>36800</v>
       </c>
@@ -6941,6 +7199,9 @@
       <c r="A163" t="s">
         <v>148</v>
       </c>
+      <c r="B163" t="s">
+        <v>499</v>
+      </c>
       <c r="D163">
         <v>34990</v>
       </c>
@@ -6955,6 +7216,9 @@
       <c r="A164" t="s">
         <v>149</v>
       </c>
+      <c r="B164" t="s">
+        <v>499</v>
+      </c>
       <c r="D164">
         <v>36800</v>
       </c>
@@ -6969,6 +7233,9 @@
       <c r="A165" t="s">
         <v>150</v>
       </c>
+      <c r="B165" t="s">
+        <v>499</v>
+      </c>
       <c r="I165">
         <v>28900</v>
       </c>
@@ -6986,6 +7253,9 @@
       <c r="A166" t="s">
         <v>151</v>
       </c>
+      <c r="B166" t="s">
+        <v>499</v>
+      </c>
       <c r="J166">
         <v>36800</v>
       </c>
@@ -7006,6 +7276,9 @@
       <c r="A167" t="s">
         <v>152</v>
       </c>
+      <c r="B167" t="s">
+        <v>499</v>
+      </c>
       <c r="J167">
         <v>36800</v>
       </c>
@@ -7026,6 +7299,9 @@
       <c r="A168" t="s">
         <v>153</v>
       </c>
+      <c r="B168" t="s">
+        <v>499</v>
+      </c>
       <c r="J168">
         <v>36800</v>
       </c>
@@ -7046,6 +7322,9 @@
       <c r="A169" t="s">
         <v>154</v>
       </c>
+      <c r="B169" t="s">
+        <v>499</v>
+      </c>
       <c r="D169">
         <v>57800</v>
       </c>
@@ -7060,6 +7339,9 @@
       <c r="A170" t="s">
         <v>155</v>
       </c>
+      <c r="B170" t="s">
+        <v>204</v>
+      </c>
       <c r="D170">
         <v>25850</v>
       </c>
@@ -7074,6 +7356,9 @@
       <c r="A171" t="s">
         <v>156</v>
       </c>
+      <c r="B171" t="s">
+        <v>204</v>
+      </c>
       <c r="D171">
         <v>25850</v>
       </c>
@@ -7088,6 +7373,9 @@
       <c r="A172" t="s">
         <v>157</v>
       </c>
+      <c r="B172" t="s">
+        <v>204</v>
+      </c>
       <c r="D172">
         <v>25850</v>
       </c>
@@ -7102,6 +7390,9 @@
       <c r="A173" t="s">
         <v>158</v>
       </c>
+      <c r="B173" t="s">
+        <v>204</v>
+      </c>
       <c r="D173">
         <v>25850</v>
       </c>
@@ -7116,6 +7407,9 @@
       <c r="A174" t="s">
         <v>159</v>
       </c>
+      <c r="B174" t="s">
+        <v>204</v>
+      </c>
       <c r="D174">
         <v>25850</v>
       </c>
@@ -7130,6 +7424,9 @@
       <c r="A175" t="s">
         <v>160</v>
       </c>
+      <c r="B175" t="s">
+        <v>204</v>
+      </c>
       <c r="D175">
         <v>25850</v>
       </c>
@@ -7144,6 +7441,9 @@
       <c r="A176" t="s">
         <v>161</v>
       </c>
+      <c r="B176" t="s">
+        <v>204</v>
+      </c>
       <c r="D176">
         <v>25850</v>
       </c>
@@ -7158,6 +7458,9 @@
       <c r="A177" t="s">
         <v>162</v>
       </c>
+      <c r="B177" t="s">
+        <v>204</v>
+      </c>
       <c r="D177">
         <v>25850</v>
       </c>
@@ -7172,6 +7475,9 @@
       <c r="A178" t="s">
         <v>163</v>
       </c>
+      <c r="B178" t="s">
+        <v>204</v>
+      </c>
       <c r="D178">
         <v>25850</v>
       </c>
@@ -7186,6 +7492,9 @@
       <c r="A179" t="s">
         <v>164</v>
       </c>
+      <c r="B179" t="s">
+        <v>204</v>
+      </c>
       <c r="D179">
         <v>12000</v>
       </c>
@@ -7203,6 +7512,9 @@
       <c r="A180" t="s">
         <v>165</v>
       </c>
+      <c r="B180" t="s">
+        <v>204</v>
+      </c>
       <c r="D180">
         <v>12000</v>
       </c>
@@ -7220,6 +7532,9 @@
       <c r="A181" t="s">
         <v>166</v>
       </c>
+      <c r="B181" t="s">
+        <v>204</v>
+      </c>
       <c r="D181">
         <v>12000</v>
       </c>
@@ -7236,6 +7551,9 @@
     <row r="182" spans="1:23" ht="255" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>167</v>
+      </c>
+      <c r="B182" t="s">
+        <v>204</v>
       </c>
       <c r="D182">
         <v>12000</v>
